--- a/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:54</t>
+    <t xml:space="preserve">2026-09-09 21:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:34</t>
+    <t xml:space="preserve">2026-09-16 21:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
@@ -6,58 +6,180 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Serie" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pais" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regiones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Serie'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Por_Edad'!$A$1:$D$18</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+  <si>
+    <t xml:space="preserve">Territorio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyectada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobertura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 13:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plot_nacional_serie_d_residentes_a_2020.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobertura de residentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile (Nacional)</t>
+  </si>
   <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de creación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16 21:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIT - MDSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagen asociada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plot_nacional_serie_d_residentes_a_2020.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobertura de residentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad territorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chile (Nacional)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarapacá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramo_Edad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5–9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10–14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15–19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20–24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25–29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30–34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35–39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40–44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45–49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50–54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55–59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60–64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65–69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70–74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75–79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80+</t>
   </si>
 </sst>
 </file>
@@ -422,8 +544,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -433,65 +557,29 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>2018</v>
+      <c r="A2" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>98.38</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>97.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="2" t="n">
+        <v>18705844</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>19458310</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>96.13</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>98.76</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>98.27</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>97.77</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:D2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -508,62 +596,588 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>347608</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>382773</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>90.81</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>864451</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>891440</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>96.97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>108913</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>107297</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>101.51</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>173429</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>178362</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>97.23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7280696</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>8125072</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>89.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>387865</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>405835</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>95.57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>243105</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>252110</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>96.43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>523969</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>511551</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>102.43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>621604</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>691854</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>89.85</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>310176</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>314709</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>98.56</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>784680</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>836096</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>93.85</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1866841</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1960170</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>95.24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>947390</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>991063</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>95.59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1079443</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1131939</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>95.36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>1562928</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1663696</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>93.94</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>988267</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1014343</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>97.43</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D17"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="12.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="12.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>984537</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1190382</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>82.71</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1251994</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1282387</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>97.63</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1239649</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1265269</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>97.98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1207885</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1260062</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>95.86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1354535</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1443181</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>93.86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1572375</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1649147</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>95.34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1562785</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1596211</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>97.91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1370451</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1435240</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>95.49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1219247</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1347007</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>90.52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1236887</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1271513</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>97.28</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1180843</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1224425</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>96.44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1161869</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1145476</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>101.43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>980475</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>989394</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>99.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>768043</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>814608</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>94.28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>599305</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>583389</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>102.73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>443305</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>413785</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>107.13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>571659</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>546834</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>104.54</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_residentes_a_2020.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 13:05</t>
+    <t xml:space="preserve">2026-10-05 05:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
